--- a/Output/Tracer-selection/Wade_rrmse_table.xlsx
+++ b/Output/Tracer-selection/Wade_rrmse_table.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
@@ -107,7 +107,22 @@
     <t xml:space="preserve">K_mg_L</t>
   </si>
   <si>
-    <t xml:space="preserve"># Dimensions</t>
+    <t xml:space="preserve">Dimensions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cl</t>
   </si>
   <si>
     <t xml:space="preserve">Mn</t>
@@ -116,22 +131,7 @@
     <t xml:space="preserve">Cu</t>
   </si>
   <si>
-    <t xml:space="preserve">Cl</t>
-  </si>
-  <si>
     <t xml:space="preserve">SO4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K</t>
   </si>
   <si>
     <t xml:space="preserve">DOC</t>
@@ -143,13 +143,14 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.00E+00"/>
+    <numFmt numFmtId="165" formatCode="0.0E+00"/>
   </numFmts>
   <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -209,12 +210,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -344,623 +349,623 @@
   <dimension ref="A1:O13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="18.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="7" style="0" width="19.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="18.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="7" style="1" width="19.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="20.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>0.840051249130851</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>0.488550569516454</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.318965508480976</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>0.312261260764494</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>0.308753916832252</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>0.301309684416922</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>0.271259697918185</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.0896377695339681</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>0.0356730835145723</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.0308607101264445</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.00353840640438573</v>
       </c>
-      <c r="O2" s="0" t="n">
+      <c r="O2" s="1" t="n">
         <v>1.10225593923609E-015</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>0.879792231343578</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>0.553060553891884</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.476164483871805</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>0.471414893774013</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>0.312728021765896</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>0.272249506181544</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>0.0327119863104981</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.0325200041578245</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.0211798666765152</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.0208635530330479</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.00636397084338387</v>
       </c>
-      <c r="O3" s="0" t="n">
+      <c r="O3" s="1" t="n">
         <v>2.11094589572383E-015</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>0.316143442605407</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>0.163895472537621</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.102512697337665</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>0.091582516257252</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>0.0889722872028047</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <v>0.0889277833625533</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="1" t="n">
         <v>0.0754565887793149</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.0672992027382864</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>0.0525594825524609</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.0363050363692404</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.0019595553398939</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4" s="1" t="n">
         <v>4.43985346336226E-016</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>0.19418632046788</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>0.158123810001817</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.12255723093744</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>0.0478265856699987</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <v>0.0419139920902357</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <v>0.02090277942175</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="1" t="n">
         <v>0.0164482968081639</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.0134808879214053</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.00628272550783778</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.000566329051743125</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.00010731656058487</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5" s="1" t="n">
         <v>6.41067578016228E-017</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>0.354526039098953</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>0.225220488579211</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.156864034387353</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>0.115506816094783</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>0.0813756526051482</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="1" t="n">
         <v>0.0704334615632312</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="1" t="n">
         <v>0.0492184997231707</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.037237180138858</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>0.0128938780893519</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.00815463566655738</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.000990137749376393</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6" s="1" t="n">
         <v>2.35425563837015E-016</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>0.112015097345771</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>0.0817559754734783</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>0.0441785947382315</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.0334919487169587</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>0.0286003499701714</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>0.0240569799315271</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.0162752188556924</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.016224600587897</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <v>0.0161513023998904</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.0120845355506582</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.00959475082148158</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7" s="1" t="n">
         <v>2.08220648761717E-016</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>0.113480172329137</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>0.0847238951747242</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>0.0443149279341126</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>0.0387207235546007</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <v>0.0359913621320734</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>0.03382493991363</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8" s="1" t="n">
         <v>0.0176498511404232</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="1" t="n">
         <v>0.0176386819580867</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <v>0.0175554701571774</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.0112635589244404</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <v>0.0110359335985869</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="O8" s="1" t="n">
         <v>1.73217274579117E-016</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>0.162799423326817</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>0.136897500651046</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>0.0916971162494317</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>0.0812940676848222</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>0.0803296461943631</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>0.0677909997332707</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J9" s="1" t="n">
         <v>0.066806970874292</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="K9" s="1" t="n">
         <v>0.0661692286329712</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="1" t="n">
         <v>0.0642644148327889</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <v>0.0412968444793377</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <v>0.00160119066028998</v>
       </c>
-      <c r="O9" s="0" t="n">
+      <c r="O9" s="1" t="n">
         <v>4.1909721018569E-016</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>0.0252513024172418</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>0.0177979278454144</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>0.0152597749151</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>0.00655550258915494</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>0.00651684467366268</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>0.00593194062438311</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J10" s="1" t="n">
         <v>0.00555935912626722</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10" s="1" t="n">
         <v>0.00549388808038626</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="1" t="n">
         <v>0.00164051669166706</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <v>0.00105562121579271</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <v>7.50332794775383E-005</v>
       </c>
-      <c r="O10" s="0" t="n">
+      <c r="O10" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>0.0332077757446893</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>0.024901011450131</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>0.0221884268539602</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>0.0091805143982974</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <v>0.00837557569960438</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>0.00468394335747324</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="J11" s="1" t="n">
         <v>0.00454665844514061</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="1" t="n">
         <v>0.00454318519833505</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="1" t="n">
         <v>0.00177185400877985</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <v>0.00130626604934714</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <v>0.000163998245885111</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="O11" s="1" t="n">
         <v>2.18262600205072E-017</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>0.191886617205792</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>0.191874424599508</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>0.0963317825237158</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <v>0.0939735868855193</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="1" t="n">
         <v>0.0925774408881522</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <v>0.057721215170346</v>
       </c>
-      <c r="J12" s="0" t="n">
+      <c r="J12" s="1" t="n">
         <v>0.0120747169897946</v>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="K12" s="1" t="n">
         <v>0.0113098437542239</v>
       </c>
-      <c r="L12" s="0" t="n">
+      <c r="L12" s="1" t="n">
         <v>0.0104850027385667</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="1" t="n">
         <v>0.00863982552891096</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="1" t="n">
         <v>0.000810977641637521</v>
       </c>
-      <c r="O12" s="0" t="n">
+      <c r="O12" s="1" t="n">
         <v>2.95712713131008E-016</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>0.48062446491098</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>0.257970447334051</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>0.173831633406987</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="1" t="n">
         <v>0.173809527648714</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="1" t="n">
         <v>0.117677328819187</v>
       </c>
-      <c r="I13" s="0" t="n">
+      <c r="I13" s="1" t="n">
         <v>0.116193688030581</v>
       </c>
-      <c r="J13" s="0" t="n">
+      <c r="J13" s="1" t="n">
         <v>0.115577818384543</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="K13" s="1" t="n">
         <v>0.0687483555829814</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="L13" s="1" t="n">
         <v>0.0614167551286617</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13" s="1" t="n">
         <v>0.0402846911513006</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="1" t="n">
         <v>0.00252739547121754</v>
       </c>
-      <c r="O13" s="0" t="n">
+      <c r="O13" s="1" t="n">
         <v>6.05961660277581E-016</v>
       </c>
     </row>
@@ -984,497 +989,497 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="0" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
+        <v>0.112015097345771</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.113480172329137</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.162799423326817</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.48062446491098</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.19418632046788</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>0.840051249130851</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="H2" s="2" t="n">
         <v>0.879792231343578</v>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>0.19418632046788</v>
-      </c>
-      <c r="E2" s="1" t="n">
+      <c r="I2" s="2" t="n">
         <v>0.354526039098953</v>
       </c>
-      <c r="F2" s="1" t="n">
-        <v>0.112015097345771</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>0.113480172329137</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>0.162799423326817</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>0.48062446491098</v>
-      </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" s="2" t="n">
+        <v>0.191886617205792</v>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>0.0252513024172418</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="L2" s="2" t="n">
         <v>0.0332077757446893</v>
       </c>
-      <c r="L2" s="1" t="n">
-        <v>0.191886617205792</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
+        <v>0.0817559754734783</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.0847238951747242</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.136897500651046</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.257970447334051</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.158123810001817</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>0.488550569516454</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="H3" s="2" t="n">
         <v>0.553060553891884</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>0.158123810001817</v>
-      </c>
-      <c r="E3" s="1" t="n">
+      <c r="I3" s="2" t="n">
         <v>0.225220488579211</v>
       </c>
-      <c r="F3" s="1" t="n">
-        <v>0.0817559754734783</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.0847238951747242</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0.136897500651046</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>0.257970447334051</v>
-      </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="2" t="n">
+        <v>0.191874424599508</v>
+      </c>
+      <c r="K3" s="2" t="n">
         <v>0.0177979278454144</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="L3" s="2" t="n">
         <v>0.024901011450131</v>
       </c>
-      <c r="L3" s="1" t="n">
-        <v>0.191874424599508</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
+        <v>0.0441785947382315</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.0443149279341126</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.0916971162494317</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.173831633406987</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.12255723093744</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>0.318965508480976</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.476164483871805</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>0.12255723093744</v>
-      </c>
-      <c r="E4" s="1" t="n">
+      <c r="I4" s="2" t="n">
         <v>0.156864034387353</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>0.0441785947382315</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.0443149279341126</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0.0916971162494317</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>0.173831633406987</v>
-      </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="2" t="n">
+        <v>0.0963317825237158</v>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>0.0152597749151</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="L4" s="2" t="n">
         <v>0.0221884268539602</v>
       </c>
-      <c r="L4" s="1" t="n">
-        <v>0.0963317825237158</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
+        <v>0.0334919487169587</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.0387207235546007</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.0812940676848222</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.173809527648714</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.0478265856699987</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>0.312261260764494</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.471414893774013</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>0.0478265856699987</v>
-      </c>
-      <c r="E5" s="1" t="n">
+      <c r="I5" s="2" t="n">
         <v>0.115506816094783</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>0.0334919487169587</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.0387207235546007</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0.0812940676848222</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0.173809527648714</v>
-      </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
+        <v>0.0939735868855193</v>
+      </c>
+      <c r="K5" s="2" t="n">
         <v>0.00655550258915494</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" s="2" t="n">
         <v>0.0091805143982974</v>
       </c>
-      <c r="L5" s="1" t="n">
-        <v>0.0939735868855193</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
+        <v>0.0286003499701714</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0.0359913621320734</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.0803296461943631</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.117677328819187</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.0419139920902357</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>0.308753916832252</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="H6" s="2" t="n">
         <v>0.312728021765896</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>0.0419139920902357</v>
-      </c>
-      <c r="E6" s="1" t="n">
+      <c r="I6" s="2" t="n">
         <v>0.0813756526051482</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>0.0286003499701714</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>0.0359913621320734</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0.0803296461943631</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>0.117677328819187</v>
-      </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
+        <v>0.0925774408881522</v>
+      </c>
+      <c r="K6" s="2" t="n">
         <v>0.00651684467366268</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="L6" s="2" t="n">
         <v>0.00837557569960438</v>
       </c>
-      <c r="L6" s="1" t="n">
-        <v>0.0925774408881522</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
+        <v>0.0240569799315271</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0.03382493991363</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.0677909997332707</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.116193688030581</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.02090277942175</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>0.301309684416922</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="H7" s="2" t="n">
         <v>0.272249506181544</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>0.02090277942175</v>
-      </c>
-      <c r="E7" s="1" t="n">
+      <c r="I7" s="2" t="n">
         <v>0.0704334615632312</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>0.0240569799315271</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>0.03382493991363</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0.0677909997332707</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>0.116193688030581</v>
-      </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
+        <v>0.057721215170346</v>
+      </c>
+      <c r="K7" s="2" t="n">
         <v>0.00593194062438311</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="L7" s="2" t="n">
         <v>0.00468394335747324</v>
       </c>
-      <c r="L7" s="1" t="n">
-        <v>0.057721215170346</v>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
+        <v>0.0162752188556924</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0.0176498511404232</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.066806970874292</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.115577818384543</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.0164482968081639</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>0.271259697918185</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.0327119863104981</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>0.0164482968081639</v>
-      </c>
-      <c r="E8" s="1" t="n">
+      <c r="I8" s="2" t="n">
         <v>0.0492184997231707</v>
       </c>
-      <c r="F8" s="1" t="n">
-        <v>0.0162752188556924</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.0176498511404232</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>0.066806970874292</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>0.115577818384543</v>
-      </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
+        <v>0.0120747169897946</v>
+      </c>
+      <c r="K8" s="2" t="n">
         <v>0.00555935912626722</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="L8" s="2" t="n">
         <v>0.00454665844514061</v>
       </c>
-      <c r="L8" s="1" t="n">
-        <v>0.0120747169897946</v>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
+        <v>0.016224600587897</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0.0176386819580867</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.0661692286329712</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.0687483555829814</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.0134808879214053</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>0.0896377695339681</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.0325200041578245</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>0.0134808879214053</v>
-      </c>
-      <c r="E9" s="1" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.037237180138858</v>
       </c>
-      <c r="F9" s="1" t="n">
-        <v>0.016224600587897</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0.0176386819580867</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0.0661692286329712</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0.0687483555829814</v>
-      </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
+        <v>0.0113098437542239</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>0.00549388808038626</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="L9" s="2" t="n">
         <v>0.00454318519833505</v>
       </c>
-      <c r="L9" s="1" t="n">
-        <v>0.0113098437542239</v>
-      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
+        <v>0.0161513023998904</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0.0175554701571774</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.0642644148327889</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.0614167551286617</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.00628272550783778</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>0.0356730835145723</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="H10" s="2" t="n">
         <v>0.0211798666765152</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>0.00628272550783778</v>
-      </c>
-      <c r="E10" s="1" t="n">
+      <c r="I10" s="2" t="n">
         <v>0.0128938780893519</v>
       </c>
-      <c r="F10" s="1" t="n">
-        <v>0.0161513023998904</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0.0175554701571774</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>0.0642644148327889</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>0.0614167551286617</v>
-      </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
+        <v>0.0104850027385667</v>
+      </c>
+      <c r="K10" s="2" t="n">
         <v>0.00164051669166706</v>
       </c>
-      <c r="K10" s="1" t="n">
+      <c r="L10" s="2" t="n">
         <v>0.00177185400877985</v>
       </c>
-      <c r="L10" s="1" t="n">
-        <v>0.0104850027385667</v>
-      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
+        <v>0.0120845355506582</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0.0112635589244404</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.0412968444793377</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.0402846911513006</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.000566329051743125</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>0.0308607101264445</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="H11" s="2" t="n">
         <v>0.0208635530330479</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>0.000566329051743125</v>
-      </c>
-      <c r="E11" s="1" t="n">
+      <c r="I11" s="2" t="n">
         <v>0.00815463566655738</v>
       </c>
-      <c r="F11" s="1" t="n">
-        <v>0.0120845355506582</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>0.0112635589244404</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>0.0412968444793377</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>0.0402846911513006</v>
-      </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
+        <v>0.00863982552891096</v>
+      </c>
+      <c r="K11" s="2" t="n">
         <v>0.00105562121579271</v>
       </c>
-      <c r="K11" s="1" t="n">
+      <c r="L11" s="2" t="n">
         <v>0.00130626604934714</v>
       </c>
-      <c r="L11" s="1" t="n">
-        <v>0.00863982552891096</v>
-      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
+        <v>0.00959475082148158</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0.0110359335985869</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.00160119066028998</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.00252739547121754</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.00010731656058487</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>0.00353840640438573</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="H12" s="2" t="n">
         <v>0.00636397084338387</v>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>0.00010731656058487</v>
-      </c>
-      <c r="E12" s="1" t="n">
+      <c r="I12" s="2" t="n">
         <v>0.000990137749376393</v>
       </c>
-      <c r="F12" s="1" t="n">
-        <v>0.00959475082148158</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>0.0110359335985869</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>0.00160119066028998</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>0.00252739547121754</v>
-      </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
+        <v>0.000810977641637521</v>
+      </c>
+      <c r="K12" s="2" t="n">
         <v>7.50332794775383E-005</v>
       </c>
-      <c r="K12" s="1" t="n">
+      <c r="L12" s="2" t="n">
         <v>0.000163998245885111</v>
       </c>
-      <c r="L12" s="1" t="n">
-        <v>0.000810977641637521</v>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
+        <v>2.08220648761717E-016</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1.73217274579117E-016</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>4.1909721018569E-016</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>6.05961660277581E-016</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>6.41067578016228E-017</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>1.10225593923609E-015</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="H13" s="2" t="n">
         <v>2.11094589572383E-015</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>6.41067578016228E-017</v>
-      </c>
-      <c r="E13" s="1" t="n">
+      <c r="I13" s="2" t="n">
         <v>2.35425563837015E-016</v>
       </c>
-      <c r="F13" s="1" t="n">
-        <v>2.08220648761717E-016</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>1.73217274579117E-016</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>4.1909721018569E-016</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>6.05961660277581E-016</v>
-      </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
+        <v>2.95712713131008E-016</v>
+      </c>
+      <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="1" t="n">
+      <c r="L13" s="2" t="n">
         <v>2.18262600205072E-017</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>2.95712713131008E-016</v>
       </c>
     </row>
   </sheetData>
